--- a/src/test/resources/TestDriver/Hearst_BIC/ActivityData/BIC_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_BIC/ActivityData/BIC_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +518,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +543,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_MGRT_US_New_75</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +573,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_MGRT_US_New_75</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +603,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +628,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,6 +658,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -618,6 +688,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,6 +718,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,6 +743,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +773,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -698,6 +803,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -718,6 +833,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -738,6 +858,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +888,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -778,6 +918,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,6 +948,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -818,6 +973,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -838,6 +1003,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -858,6 +1033,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -878,6 +1063,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -898,6 +1088,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_45</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -918,6 +1118,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_45</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -938,6 +1148,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_45</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -958,6 +1178,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -978,6 +1203,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -998,6 +1233,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1263,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1038,6 +1293,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1058,6 +1318,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1078,6 +1348,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1098,6 +1378,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1118,6 +1408,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1138,6 +1433,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_55</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1158,6 +1463,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_55</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1178,6 +1493,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_55</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1523,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1218,6 +1548,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_5999</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1238,6 +1578,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_5999</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1258,6 +1608,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_5999</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1278,6 +1638,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1298,6 +1663,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1318,6 +1693,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1338,6 +1723,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1358,6 +1753,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1378,6 +1778,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1398,6 +1808,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1418,6 +1838,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BIC_PREM_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1438,6 +1868,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1458,6 +1893,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1478,6 +1923,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1498,6 +1953,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1518,6 +1978,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1538,6 +2008,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1558,6 +2038,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1578,6 +2063,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1598,6 +2088,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1618,6 +2118,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1638,6 +2148,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1658,6 +2173,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1678,6 +2203,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1698,6 +2233,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1718,6 +2258,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_GIFT_US_3999</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1738,6 +2288,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_GIFT_US_3999</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1758,6 +2318,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1778,6 +2343,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_MGRT_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1798,6 +2373,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_MGRT_CAN_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1818,6 +2403,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1838,6 +2428,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1858,6 +2458,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1878,6 +2488,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1898,6 +2513,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1918,6 +2543,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1938,6 +2573,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1958,6 +2598,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1978,6 +2628,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1998,6 +2658,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2018,6 +2683,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_25</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2038,6 +2713,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_25</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2058,6 +2743,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2078,6 +2768,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2098,6 +2798,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2118,6 +2828,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2138,6 +2853,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2158,6 +2883,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2178,6 +2913,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2198,6 +2938,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2218,6 +2968,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2238,6 +2998,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2258,6 +3023,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2278,6 +3053,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_3999</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2298,6 +3083,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2318,6 +3108,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2338,6 +3138,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_New_40</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2358,6 +3168,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2378,6 +3193,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2398,6 +3223,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>BIC_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2418,6 +3253,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2436,6 +3276,11 @@
       <c r="D101" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
